--- a/mosip_master/xlsx/valid_document.xlsx
+++ b/mosip_master/xlsx/valid_document.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ganesh\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF62E7C4-862A-41DD-9DF6-7F201C949FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCF9F7D-6CA6-4605-8259-D0B0A596DB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$15</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>doctyp_code</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>CBT</t>
-  </si>
-  <si>
-    <t>ACM</t>
   </si>
   <si>
     <t>CCM</t>
@@ -186,9 +183,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -226,7 +223,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -332,7 +329,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -474,7 +471,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -482,17 +479,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="1"/>
-    <col min="1023" max="1024" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" style="1"/>
+    <col min="1023" max="1024" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -506,7 +503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -520,7 +517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -534,7 +531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -548,12 +545,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -562,12 +559,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -576,9 +573,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -590,9 +587,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -604,9 +601,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -618,9 +615,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -632,9 +629,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -646,12 +643,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -660,12 +657,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -674,12 +671,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
@@ -688,8 +685,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15" t="s">
@@ -702,22 +699,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D15" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/mosip_master/xlsx/valid_document.xlsx
+++ b/mosip_master/xlsx/valid_document.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCF9F7D-6CA6-4605-8259-D0B0A596DB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8919A7-5FD3-4314-A433-B6B15A13E651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>doctyp_code</t>
   </si>
@@ -48,9 +48,6 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>POA</t>
-  </si>
-  <si>
     <t>POR</t>
   </si>
   <si>
@@ -60,36 +57,15 @@
     <t>por</t>
   </si>
   <si>
-    <t>ARE</t>
-  </si>
-  <si>
-    <t>CEA</t>
-  </si>
-  <si>
-    <t>CTL</t>
-  </si>
-  <si>
-    <t>ASN</t>
-  </si>
-  <si>
     <t>BID</t>
   </si>
   <si>
-    <t>CDC</t>
-  </si>
-  <si>
     <t>PAS</t>
   </si>
   <si>
-    <t>CVE</t>
-  </si>
-  <si>
     <t>CED</t>
   </si>
   <si>
-    <t>CBT</t>
-  </si>
-  <si>
     <t>CCM</t>
   </si>
   <si>
@@ -100,6 +76,9 @@
   </si>
   <si>
     <t>BLS</t>
+  </si>
+  <si>
+    <t>DSN</t>
   </si>
 </sst>
 </file>
@@ -479,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.90625" customWidth="1"/>
@@ -505,13 +484,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -519,13 +498,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -533,13 +512,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>5</v>
@@ -547,13 +526,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>5</v>
@@ -561,13 +540,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>5</v>
@@ -575,13 +554,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>5</v>
@@ -589,118 +568,34 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
+      <c r="A9" t="s">
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D15" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D9" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
